--- a/studies/AI ranking test/data for thesis/data partition.xlsx
+++ b/studies/AI ranking test/data for thesis/data partition.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\用完就刪\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R\Thesis\studies\AI ranking test\data for thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EEDF473-AE94-4D8B-ADC2-386BAD3971C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223D9908-0667-44BA-AB90-3B5B6AD3C5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E5A551B8-79B9-4C2C-9E1E-B1C876A2B4FE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Many of us dream of one day travelling to as beautiful a country as Japan, yet we often get so caught up in our fantasies of what we would like to do once we're there that we neglect to consider just how we will get there. With this short guide, you will be able to navigate through any of Japan's airport! First, make sure that you have your passport in order, as this will be your most important means of identification, so be sure to always carry it with you and to keep it safe. Once your arrive at the airport, follow signs for check-in and go through security. Japan's airports have various public transport links to help you find and navigate your way, shuttling you through the vast complex directly to your desired destination. There are also maps to ensure that you never lose your way. Listen for boarding announcements and follow staff instructions. You will reach board the plane in no time!</t>
   </si>
@@ -467,10 +467,7 @@
 check in and present your ID and booking details.  Check in your luggage, and receive your boarding pass.  Next, there is security screening.  Proceed to the security checkpoint. Remove shoes, belts, and electronics from carry-ons.  Continue with security check and pass through the metal detector or body scanner. Collect your belongings.  Then, check your boarding pass and airport monitors for your gate number. Follow signs to your gate.  Wait and arrive at the gate early. Use this time to grab snacks or use the restroom.  Finally, you will board and listen for boarding announcements. Board when your group is called and present your boarding pass.  Follow these steps to ensure a smooth airport experience.</t>
   </si>
   <si>
-    <t>Practical Task Description</t>
-  </si>
-  <si>
-    <t>You are preparing a post for your Facebook fan page that will guide first-time travelers successfully through the complicated process at a major airport in Japan to travel. The Facebook post will be divided into two parts.
+    <t>Practical Task Description——You are preparing a post for your Facebook fan page that will guide first-time travelers successfully through the complicated process at a major airport in Japan to travel. The Facebook post will be divided into two parts.
 Part 1: Create a concise, step-by-step guide that a traveler needs to follow from the moment they arrive at the airport until they board their plane. A traveler should be able to navigate the airport experience following only your guide. The guide should be 100–200 words.
 Part 2: Highlight the top three bits of advice you would give travelers to prevent the most common mistakes they might make. Each of the three bits of advice should be no more than 1 sentence (three sentences total).</t>
   </si>
@@ -1466,13 +1463,11 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="B1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
